--- a/artfynd/A 55304-2024 artfynd.xlsx
+++ b/artfynd/A 55304-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -809,6 +809,538 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128629718</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56571</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hultetvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>547055</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6321797</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128629713</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56558</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100086</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dammfladdermus</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Myotis dasycneme</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(F.Boie, 1825)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hultetvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>547055</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6321797</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128629715</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56573</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hultetvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>547055</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6321797</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128629716</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56552</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hultetvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>547055</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6321797</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55304-2024 artfynd.xlsx
+++ b/artfynd/A 55304-2024 artfynd.xlsx
@@ -812,37 +812,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128629718</v>
+        <v>128629713</v>
       </c>
       <c r="B3" t="n">
-        <v>56571</v>
+        <v>56562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>100086</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Dammfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis dasycneme</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(F.Boie, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -945,37 +945,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128629713</v>
+        <v>128629718</v>
       </c>
       <c r="B4" t="n">
-        <v>56558</v>
+        <v>56575</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100086</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dammfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Myotis dasycneme</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(F.Boie, 1825)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1081,7 +1081,7 @@
         <v>128629715</v>
       </c>
       <c r="B5" t="n">
-        <v>56573</v>
+        <v>56577</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>128629716</v>
       </c>
       <c r="B6" t="n">
-        <v>56552</v>
+        <v>56556</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 55304-2024 artfynd.xlsx
+++ b/artfynd/A 55304-2024 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>128629713</v>
       </c>
       <c r="B3" t="n">
-        <v>56562</v>
+        <v>56589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>128629718</v>
       </c>
       <c r="B4" t="n">
-        <v>56575</v>
+        <v>56602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>128629715</v>
       </c>
       <c r="B5" t="n">
-        <v>56577</v>
+        <v>56604</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>128629716</v>
       </c>
       <c r="B6" t="n">
-        <v>56556</v>
+        <v>56583</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 55304-2024 artfynd.xlsx
+++ b/artfynd/A 55304-2024 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>128629713</v>
       </c>
       <c r="B3" t="n">
-        <v>56589</v>
+        <v>56592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>128629718</v>
       </c>
       <c r="B4" t="n">
-        <v>56602</v>
+        <v>56605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>128629715</v>
       </c>
       <c r="B5" t="n">
-        <v>56604</v>
+        <v>56607</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>128629716</v>
       </c>
       <c r="B6" t="n">
-        <v>56583</v>
+        <v>56586</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 55304-2024 artfynd.xlsx
+++ b/artfynd/A 55304-2024 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>128629713</v>
       </c>
       <c r="B3" t="n">
-        <v>56592</v>
+        <v>56595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>128629718</v>
       </c>
       <c r="B4" t="n">
-        <v>56605</v>
+        <v>56608</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>128629715</v>
       </c>
       <c r="B5" t="n">
-        <v>56607</v>
+        <v>56610</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>128629716</v>
       </c>
       <c r="B6" t="n">
-        <v>56586</v>
+        <v>56589</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 55304-2024 artfynd.xlsx
+++ b/artfynd/A 55304-2024 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>128629713</v>
       </c>
       <c r="B3" t="n">
-        <v>56595</v>
+        <v>56597</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>128629718</v>
       </c>
       <c r="B4" t="n">
-        <v>56608</v>
+        <v>56610</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>128629715</v>
       </c>
       <c r="B5" t="n">
-        <v>56610</v>
+        <v>56612</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>128629716</v>
       </c>
       <c r="B6" t="n">
-        <v>56589</v>
+        <v>56591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
